--- a/Calibration/Winch Calibration Curve/Winch Calibration Curve.xlsx
+++ b/Calibration/Winch Calibration Curve/Winch Calibration Curve.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://djpropertycom-my.sharepoint.com/personal/noah_familiajones_org/Documents/Work and Projects/Github/Bio-Inspired-Sensing/Calibration/Winch Calibration Curve/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="598" documentId="11_F25DC773A252ABDACC10483729DA651C5BDE58E9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6E3DBDAF-E15B-4F17-A943-764FFAE02A18}"/>
+  <xr:revisionPtr revIDLastSave="602" documentId="11_F25DC773A252ABDACC10483729DA651C5BDE58E9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{53C5AE62-140F-4702-9B3F-C11A02A4F557}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -741,13 +741,7 @@
   <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="2" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -760,29 +754,17 @@
     <xf numFmtId="164" fontId="2" fillId="8" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="2" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="2" fontId="2" fillId="7" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -935,6 +917,24 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1411,6 +1411,12 @@
           <c:dLbls>
             <c:dLbl>
               <c:idx val="0"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-3.1231231231231144E-2"/>
+                  <c:y val="3.8889006756125714E-2"/>
+                </c:manualLayout>
+              </c:layout>
               <c:tx>
                 <c:rich>
                   <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
@@ -1470,9 +1476,14 @@
               <c:showSerName val="0"/>
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
-              <c:separator/>
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout>
+                    <c:manualLayout>
+                      <c:w val="0.24791544300205717"/>
+                      <c:h val="9.650002110674126E-2"/>
+                    </c:manualLayout>
+                  </c15:layout>
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -1515,7 +1526,6 @@
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
-            <c:separator/>
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
@@ -2444,14 +2454,14 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>428625</xdr:colOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
       <xdr:row>53</xdr:row>
-      <xdr:rowOff>171450</xdr:rowOff>
+      <xdr:rowOff>171449</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2477,6 +2487,10 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2742,7 +2756,7 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="0" width="350" row="8">
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="6">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
 </wetp:taskpanes>
@@ -2778,51 +2792,51 @@
   <sheetData>
     <row r="1" spans="1:8" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
-      <c r="B1" s="14"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="10" t="s">
+      <c r="B1" s="10"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="72" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="11"/>
-      <c r="H1" s="18"/>
+      <c r="G1" s="73"/>
+      <c r="H1" s="74"/>
     </row>
     <row r="2" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
-      <c r="B2" s="15"/>
+      <c r="B2" s="11"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="75" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="3"/>
-      <c r="H2" s="19"/>
+      <c r="G2" s="76"/>
+      <c r="H2" s="77"/>
     </row>
     <row r="3" spans="1:8" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="39" t="s">
+      <c r="B3" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="40" t="s">
+      <c r="C3" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="40" t="s">
+      <c r="D3" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="41" t="s">
+      <c r="E3" s="35" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="42" t="s">
+      <c r="F3" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="43" t="s">
+      <c r="G3" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="44" t="s">
+      <c r="H3" s="38" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2831,526 +2845,526 @@
         <f>4.86</f>
         <v>4.8600000000000003</v>
       </c>
-      <c r="B4" s="32">
+      <c r="B4" s="26">
         <f>(A4/1000)*9.81</f>
         <v>4.7676600000000006E-2</v>
       </c>
-      <c r="C4" s="33">
+      <c r="C4" s="27">
         <v>20</v>
       </c>
-      <c r="D4" s="34">
+      <c r="D4" s="28">
         <f>(C4/1000)*9.81</f>
         <v>0.19620000000000001</v>
       </c>
-      <c r="E4" s="35">
+      <c r="E4" s="29">
         <f>$B$4+D4</f>
         <v>0.24387660000000003</v>
       </c>
-      <c r="F4" s="36">
+      <c r="F4" s="30">
         <v>0.27</v>
       </c>
-      <c r="G4" s="37">
+      <c r="G4" s="31">
         <v>0.28000000000000003</v>
       </c>
-      <c r="H4" s="38">
+      <c r="H4" s="32">
         <v>0.27</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
-      <c r="B5" s="16"/>
-      <c r="C5" s="7">
+      <c r="B5" s="12"/>
+      <c r="C5" s="5">
         <v>40</v>
       </c>
-      <c r="D5" s="8">
+      <c r="D5" s="6">
         <f t="shared" ref="D5:D11" si="0">(C5/1000)*9.81</f>
         <v>0.39240000000000003</v>
       </c>
-      <c r="E5" s="24">
+      <c r="E5" s="18">
         <f t="shared" ref="E5:E11" si="1">$B$4+D5</f>
         <v>0.44007660000000004</v>
       </c>
-      <c r="F5" s="30">
+      <c r="F5" s="24">
         <v>0.46</v>
       </c>
-      <c r="G5" s="27">
+      <c r="G5" s="21">
         <v>0.37</v>
       </c>
-      <c r="H5" s="21">
+      <c r="H5" s="15">
         <v>0.47</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
-      <c r="B6" s="16"/>
-      <c r="C6" s="5">
+      <c r="B6" s="12"/>
+      <c r="C6" s="3">
         <v>60</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="4">
         <f t="shared" si="0"/>
         <v>0.58860000000000001</v>
       </c>
-      <c r="E6" s="23">
+      <c r="E6" s="17">
         <f t="shared" si="1"/>
         <v>0.63627659999999997</v>
       </c>
-      <c r="F6" s="29">
+      <c r="F6" s="23">
         <v>0.63</v>
       </c>
-      <c r="G6" s="26">
+      <c r="G6" s="20">
         <v>0.65</v>
       </c>
-      <c r="H6" s="20">
+      <c r="H6" s="14">
         <v>0.62</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
-      <c r="B7" s="16"/>
-      <c r="C7" s="7">
+      <c r="B7" s="12"/>
+      <c r="C7" s="5">
         <v>80</v>
       </c>
-      <c r="D7" s="8">
+      <c r="D7" s="6">
         <f t="shared" si="0"/>
         <v>0.78480000000000005</v>
       </c>
-      <c r="E7" s="24">
+      <c r="E7" s="18">
         <f t="shared" si="1"/>
         <v>0.83247660000000001</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="24">
         <v>0.86</v>
       </c>
-      <c r="G7" s="27">
+      <c r="G7" s="21">
         <v>0.77</v>
       </c>
-      <c r="H7" s="21">
+      <c r="H7" s="15">
         <v>0.79</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
-      <c r="B8" s="16"/>
-      <c r="C8" s="5">
+      <c r="B8" s="12"/>
+      <c r="C8" s="3">
         <v>100</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="4">
         <f t="shared" si="0"/>
         <v>0.98100000000000009</v>
       </c>
-      <c r="E8" s="23">
+      <c r="E8" s="17">
         <f t="shared" si="1"/>
         <v>1.0286766000000001</v>
       </c>
-      <c r="F8" s="29">
+      <c r="F8" s="23">
         <v>0.98</v>
       </c>
-      <c r="G8" s="26">
+      <c r="G8" s="20">
         <v>1.01</v>
       </c>
-      <c r="H8" s="20">
+      <c r="H8" s="14">
         <v>0.95</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
-      <c r="B9" s="16"/>
-      <c r="C9" s="7">
+      <c r="B9" s="12"/>
+      <c r="C9" s="5">
         <v>110</v>
       </c>
-      <c r="D9" s="8">
+      <c r="D9" s="6">
         <f t="shared" si="0"/>
         <v>1.0791000000000002</v>
       </c>
-      <c r="E9" s="24">
+      <c r="E9" s="18">
         <f t="shared" si="1"/>
         <v>1.1267766000000001</v>
       </c>
-      <c r="F9" s="30">
+      <c r="F9" s="24">
         <v>1.08</v>
       </c>
-      <c r="G9" s="27">
+      <c r="G9" s="21">
         <v>1.07</v>
       </c>
-      <c r="H9" s="21">
+      <c r="H9" s="15">
         <v>1.0900000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
-      <c r="B10" s="16"/>
-      <c r="C10" s="5">
+      <c r="B10" s="12"/>
+      <c r="C10" s="3">
         <v>130</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="4">
         <f t="shared" si="0"/>
         <v>1.2753000000000001</v>
       </c>
-      <c r="E10" s="23">
+      <c r="E10" s="17">
         <f t="shared" si="1"/>
         <v>1.3229766000000001</v>
       </c>
-      <c r="F10" s="29">
+      <c r="F10" s="23">
         <v>1.27</v>
       </c>
-      <c r="G10" s="26">
+      <c r="G10" s="20">
         <v>1.26</v>
       </c>
-      <c r="H10" s="20">
+      <c r="H10" s="14">
         <v>1.3</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
-      <c r="B11" s="17"/>
-      <c r="C11" s="12">
+      <c r="B11" s="13"/>
+      <c r="C11" s="8">
         <v>150</v>
       </c>
-      <c r="D11" s="13">
+      <c r="D11" s="9">
         <f t="shared" si="0"/>
         <v>1.4715</v>
       </c>
-      <c r="E11" s="25">
+      <c r="E11" s="19">
         <f t="shared" si="1"/>
         <v>1.5191766</v>
       </c>
-      <c r="F11" s="31">
+      <c r="F11" s="25">
         <v>1.47</v>
       </c>
-      <c r="G11" s="28">
+      <c r="G11" s="22">
         <v>1.44</v>
       </c>
-      <c r="H11" s="22">
+      <c r="H11" s="16">
         <v>1.43</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="15.75" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="75" t="s">
+      <c r="B13" s="69" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:8" s="46" customFormat="1" ht="30" customHeight="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="59" t="s">
+    <row r="14" spans="1:8" s="40" customFormat="1" ht="30" customHeight="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="53" t="s">
         <v>10</v>
       </c>
-      <c r="C14" s="60" t="s">
+      <c r="C14" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="D14" s="60" t="s">
+      <c r="D14" s="54" t="s">
         <v>12</v>
       </c>
-      <c r="E14" s="60" t="s">
+      <c r="E14" s="54" t="s">
         <v>13</v>
       </c>
-      <c r="F14" s="61" t="s">
+      <c r="F14" s="55" t="s">
         <v>14</v>
       </c>
-      <c r="G14" s="76" t="s">
+      <c r="G14" s="70" t="s">
         <v>29</v>
       </c>
-      <c r="H14" s="76" t="s">
+      <c r="H14" s="70" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="15" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="56">
-        <f>E4</f>
+      <c r="B15" s="50">
+        <f t="shared" ref="B15:B22" si="2">E4</f>
         <v>0.24387660000000003</v>
       </c>
-      <c r="C15" s="57">
-        <f>AVERAGE(F4:H4)</f>
+      <c r="C15" s="51">
+        <f t="shared" ref="C15:C22" si="3">AVERAGE(F4:H4)</f>
         <v>0.27333333333333337</v>
       </c>
-      <c r="D15" s="57">
-        <f>STDEV(F4:H4)</f>
+      <c r="D15" s="51">
+        <f t="shared" ref="D15:D22" si="4">STDEV(F4:H4)</f>
         <v>5.7735026918962623E-3</v>
       </c>
-      <c r="E15" s="57">
-        <f>E4</f>
+      <c r="E15" s="51">
+        <f t="shared" ref="E15:E22" si="5">E4</f>
         <v>0.24387660000000003</v>
       </c>
-      <c r="F15" s="58">
-        <f>$C$28*B15+$C$29</f>
+      <c r="F15" s="52">
+        <f t="shared" ref="F15:F22" si="6">$C$28*B15+$C$29</f>
         <v>0.26289544235924944</v>
       </c>
-      <c r="G15" s="77">
+      <c r="G15" s="71">
         <v>1.25</v>
       </c>
-      <c r="H15" s="77">
+      <c r="H15" s="71">
         <v>0.4</v>
       </c>
     </row>
     <row r="16" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="51">
-        <f>E5</f>
+      <c r="B16" s="45">
+        <f t="shared" si="2"/>
         <v>0.44007660000000004</v>
       </c>
-      <c r="C16" s="48">
-        <f>AVERAGE(F5:H5)</f>
+      <c r="C16" s="42">
+        <f t="shared" si="3"/>
         <v>0.43333333333333335</v>
       </c>
-      <c r="D16" s="48">
-        <f>STDEV(F5:H5)</f>
+      <c r="D16" s="42">
+        <f t="shared" si="4"/>
         <v>5.507570547286101E-2</v>
       </c>
-      <c r="E16" s="48">
-        <f>E5</f>
+      <c r="E16" s="42">
+        <f t="shared" si="5"/>
         <v>0.44007660000000004</v>
       </c>
-      <c r="F16" s="54">
-        <f>$C$28*B16+$C$29</f>
+      <c r="F16" s="48">
+        <f t="shared" si="6"/>
         <v>0.44504021447721187</v>
       </c>
     </row>
     <row r="17" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="50">
-        <f>E6</f>
+      <c r="B17" s="44">
+        <f t="shared" si="2"/>
         <v>0.63627659999999997</v>
       </c>
-      <c r="C17" s="47">
-        <f>AVERAGE(F6:H6)</f>
+      <c r="C17" s="41">
+        <f t="shared" si="3"/>
         <v>0.6333333333333333</v>
       </c>
-      <c r="D17" s="47">
-        <f>STDEV(F6:H6)</f>
+      <c r="D17" s="41">
+        <f t="shared" si="4"/>
         <v>1.527525231651948E-2</v>
       </c>
-      <c r="E17" s="47">
-        <f>E6</f>
+      <c r="E17" s="41">
+        <f t="shared" si="5"/>
         <v>0.63627659999999997</v>
       </c>
-      <c r="F17" s="53">
-        <f>$C$28*B17+$C$29</f>
+      <c r="F17" s="47">
+        <f t="shared" si="6"/>
         <v>0.6271849865951743</v>
       </c>
     </row>
     <row r="18" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="51">
-        <f>E7</f>
+      <c r="B18" s="45">
+        <f t="shared" si="2"/>
         <v>0.83247660000000001</v>
       </c>
-      <c r="C18" s="48">
-        <f>AVERAGE(F7:H7)</f>
+      <c r="C18" s="42">
+        <f t="shared" si="3"/>
         <v>0.80666666666666664</v>
       </c>
-      <c r="D18" s="48">
-        <f>STDEV(F7:H7)</f>
+      <c r="D18" s="42">
+        <f t="shared" si="4"/>
         <v>4.7258156262526066E-2</v>
       </c>
-      <c r="E18" s="48">
-        <f>E7</f>
+      <c r="E18" s="42">
+        <f t="shared" si="5"/>
         <v>0.83247660000000001</v>
       </c>
-      <c r="F18" s="54">
-        <f>$C$28*B18+$C$29</f>
+      <c r="F18" s="48">
+        <f t="shared" si="6"/>
         <v>0.80932975871313673</v>
       </c>
     </row>
     <row r="19" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="50">
-        <f>E8</f>
+      <c r="B19" s="44">
+        <f t="shared" si="2"/>
         <v>1.0286766000000001</v>
       </c>
-      <c r="C19" s="47">
-        <f>AVERAGE(F8:H8)</f>
+      <c r="C19" s="41">
+        <f t="shared" si="3"/>
         <v>0.98</v>
       </c>
-      <c r="D19" s="47">
-        <f>STDEV(F8:H8)</f>
+      <c r="D19" s="41">
+        <f t="shared" si="4"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="E19" s="47">
-        <f>E8</f>
+      <c r="E19" s="41">
+        <f t="shared" si="5"/>
         <v>1.0286766000000001</v>
       </c>
-      <c r="F19" s="53">
-        <f>$C$28*B19+$C$29</f>
+      <c r="F19" s="47">
+        <f t="shared" si="6"/>
         <v>0.99147453083109915</v>
       </c>
     </row>
     <row r="20" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="51">
-        <f>E9</f>
+      <c r="B20" s="45">
+        <f t="shared" si="2"/>
         <v>1.1267766000000001</v>
       </c>
-      <c r="C20" s="48">
-        <f>AVERAGE(F9:H9)</f>
+      <c r="C20" s="42">
+        <f t="shared" si="3"/>
         <v>1.08</v>
       </c>
-      <c r="D20" s="48">
-        <f>STDEV(F9:H9)</f>
+      <c r="D20" s="42">
+        <f t="shared" si="4"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="E20" s="48">
-        <f>E9</f>
+      <c r="E20" s="42">
+        <f t="shared" si="5"/>
         <v>1.1267766000000001</v>
       </c>
-      <c r="F20" s="54">
-        <f>$C$28*B20+$C$29</f>
+      <c r="F20" s="48">
+        <f t="shared" si="6"/>
         <v>1.0825469168900805</v>
       </c>
     </row>
     <row r="21" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="50">
-        <f>E10</f>
+      <c r="B21" s="44">
+        <f t="shared" si="2"/>
         <v>1.3229766000000001</v>
       </c>
-      <c r="C21" s="47">
-        <f>AVERAGE(F10:H10)</f>
+      <c r="C21" s="41">
+        <f t="shared" si="3"/>
         <v>1.2766666666666666</v>
       </c>
-      <c r="D21" s="47">
-        <f>STDEV(F10:H10)</f>
+      <c r="D21" s="41">
+        <f t="shared" si="4"/>
         <v>2.0816659994661344E-2</v>
       </c>
-      <c r="E21" s="47">
-        <f>E10</f>
+      <c r="E21" s="41">
+        <f t="shared" si="5"/>
         <v>1.3229766000000001</v>
       </c>
-      <c r="F21" s="53">
-        <f>$C$28*B21+$C$29</f>
+      <c r="F21" s="47">
+        <f t="shared" si="6"/>
         <v>1.2646916890080426</v>
       </c>
     </row>
     <row r="22" spans="2:6" ht="15.75" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="52">
-        <f>E11</f>
+      <c r="B22" s="46">
+        <f t="shared" si="2"/>
         <v>1.5191766</v>
       </c>
-      <c r="C22" s="49">
-        <f>AVERAGE(F11:H11)</f>
+      <c r="C22" s="43">
+        <f t="shared" si="3"/>
         <v>1.4466666666666665</v>
       </c>
-      <c r="D22" s="49">
-        <f>STDEV(F11:H11)</f>
+      <c r="D22" s="43">
+        <f t="shared" si="4"/>
         <v>2.0816659994661344E-2</v>
       </c>
-      <c r="E22" s="49">
-        <f>E11</f>
+      <c r="E22" s="43">
+        <f t="shared" si="5"/>
         <v>1.5191766</v>
       </c>
-      <c r="F22" s="55">
-        <f>$C$28*B22+$C$29</f>
+      <c r="F22" s="49">
+        <f t="shared" si="6"/>
         <v>1.4468364611260052</v>
       </c>
     </row>
     <row r="24" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="25" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B25" s="62" t="s">
+      <c r="B25" s="56" t="s">
         <v>15</v>
       </c>
-      <c r="C25" s="68"/>
-      <c r="D25" s="45"/>
-      <c r="E25" s="45"/>
-      <c r="F25" s="45"/>
+      <c r="C25" s="62"/>
+      <c r="D25" s="39"/>
+      <c r="E25" s="39"/>
+      <c r="F25" s="39"/>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B26" s="63"/>
-      <c r="C26" s="69"/>
+      <c r="B26" s="57"/>
+      <c r="C26" s="63"/>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B27" s="64" t="s">
+      <c r="B27" s="58" t="s">
         <v>16</v>
       </c>
-      <c r="C27" s="69"/>
+      <c r="C27" s="63"/>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B28" s="65" t="s">
+      <c r="B28" s="59" t="s">
         <v>17</v>
       </c>
-      <c r="C28" s="70">
+      <c r="C28" s="64">
         <f>SLOPE(C15:C22,B15:B22)</f>
         <v>0.92836275289481363</v>
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B29" s="65" t="s">
+      <c r="B29" s="59" t="s">
         <v>18</v>
       </c>
-      <c r="C29" s="70">
+      <c r="C29" s="64">
         <f>INTERCEPT(C15:C22,B15:B22)</f>
         <v>3.64894906166221E-2</v>
       </c>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B30" s="65" t="s">
+      <c r="B30" s="59" t="s">
         <v>19</v>
       </c>
-      <c r="C30" s="71">
+      <c r="C30" s="65">
         <f>RSQ(C15:C22,B15:B22)</f>
         <v>0.99950679318571178</v>
       </c>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B31" s="66"/>
-      <c r="C31" s="72"/>
+      <c r="B31" s="60"/>
+      <c r="C31" s="66"/>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B32" s="64" t="s">
+      <c r="B32" s="58" t="s">
         <v>20</v>
       </c>
-      <c r="C32" s="69"/>
+      <c r="C32" s="63"/>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B33" s="65" t="s">
+      <c r="B33" s="59" t="s">
         <v>21</v>
       </c>
-      <c r="C33" s="70">
+      <c r="C33" s="64">
         <f>AVERAGE(ABS(C15-B15),ABS(C16-B16),ABS(C17-B17),ABS(C18-B18),ABS(C19-B19),ABS(C20-B20),ABS(C21-B21),ABS(C22-B22))</f>
         <v>3.4903283333333382E-2</v>
       </c>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B34" s="65" t="s">
+      <c r="B34" s="59" t="s">
         <v>22</v>
       </c>
-      <c r="C34" s="70">
+      <c r="C34" s="64">
         <f>SQRT(AVERAGE((C15-B15)^2,(C16-B16)^2,(C17-B17)^2,(C18-B18)^2,(C19-B19)^2,(C20-B20)^2,(C21-B21)^2,(C22-B22)^2))</f>
         <v>4.115177443594227E-2</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B35" s="65" t="s">
+      <c r="B35" s="59" t="s">
         <v>23</v>
       </c>
-      <c r="C35" s="70">
+      <c r="C35" s="64">
         <f>MAX(ABS(C15-B15),ABS(C16-B16),ABS(C17-B17),ABS(C18-B18),ABS(C19-B19),ABS(C20-B20),ABS(C21-B21),ABS(C22-B22))</f>
         <v>7.2509933333333443E-2</v>
       </c>
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B36" s="65" t="s">
+      <c r="B36" s="59" t="s">
         <v>24</v>
       </c>
-      <c r="C36" s="73">
+      <c r="C36" s="67">
         <f>AVERAGE(ABS(C15-B15)/B15,ABS(C16-B16)/B16,ABS(C17-B17)/B17,ABS(C18-B18)/B18,ABS(C19-B19)/B19,ABS(C20-B20)/B20,ABS(C21-B21)/B21,ABS(C22-B22)/B22)*100</f>
         <v>4.2913160528430172</v>
       </c>
     </row>
     <row r="37" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B37" s="66"/>
-      <c r="C37" s="72"/>
+      <c r="B37" s="60"/>
+      <c r="C37" s="66"/>
     </row>
     <row r="38" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B38" s="64" t="s">
+      <c r="B38" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="C38" s="69"/>
+      <c r="C38" s="63"/>
     </row>
     <row r="39" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B39" s="65" t="s">
+      <c r="B39" s="59" t="s">
         <v>26</v>
       </c>
-      <c r="C39" s="70">
+      <c r="C39" s="64">
         <f>AVERAGE(D15:D22)</f>
         <v>2.5626992091640689E-2</v>
       </c>
     </row>
     <row r="40" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B40" s="67" t="s">
+      <c r="B40" s="61" t="s">
         <v>27</v>
       </c>
-      <c r="C40" s="74">
+      <c r="C40" s="68">
         <f>AVERAGE(D15/C15,D16/C16,D17/C17,D18/C18,D19/C19,D20/C20,D21/C21,D22/C22)*100</f>
         <v>3.7686255204453829</v>
       </c>

--- a/Calibration/Winch Calibration Curve/Winch Calibration Curve.xlsx
+++ b/Calibration/Winch Calibration Curve/Winch Calibration Curve.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://djpropertycom-my.sharepoint.com/personal/noah_familiajones_org/Documents/Work and Projects/Github/Bio-Inspired-Sensing/Calibration/Winch Calibration Curve/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="602" documentId="11_F25DC773A252ABDACC10483729DA651C5BDE58E9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{53C5AE62-140F-4702-9B3F-C11A02A4F557}"/>
+  <xr:revisionPtr revIDLastSave="607" documentId="11_F25DC773A252ABDACC10483729DA651C5BDE58E9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A1CF88F0-8949-471D-A277-474988ACAD37}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,6 +17,9 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
+      <x14:workbookPr defaultImageDpi="32767"/>
+    </ext>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
@@ -1821,6 +1824,10 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
+      <c:legendEntry>
+        <c:idx val="3"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1866,9 +1873,7 @@
       <a:schemeClr val="bg1"/>
     </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:srgbClr val="1F4E79"/>
-      </a:solidFill>
+      <a:noFill/>
       <a:prstDash val="solid"/>
       <a:round/>
     </a:ln>
